--- a/Documents/Deliverables_LB/BOM/LED Board (LB)_DigiKey.xlsx
+++ b/Documents/Deliverables_LB/BOM/LED Board (LB)_DigiKey.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\FranciscoGimenez-HCDSHardware\Documents\Deliverables_LB\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555EDAEE-A93B-47B0-AB5E-3F92CB86CE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8612894-7785-47CD-9682-429A1E6A18A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9702A19A-E861-442A-8D87-5A6EE6F71E37}"/>
+    <workbookView xWindow="2805" yWindow="2805" windowWidth="10335" windowHeight="7830" xr2:uid="{9702A19A-E861-442A-8D87-5A6EE6F71E37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>S. No.</t>
   </si>
@@ -100,9 +100,6 @@
     <t>LED</t>
   </si>
   <si>
-    <t>Resistor</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total Component Cost </t>
   </si>
   <si>
@@ -112,34 +109,56 @@
     <t>Bill of Material (BOM) for  LED Board</t>
   </si>
   <si>
-    <t>200R</t>
-  </si>
-  <si>
-    <t>LED1, LED2, LED3, LED4, LED5, LED6, LED7, LED8, LED9, LED10, LED11, LED12, LED13, LED14, LED15, LED16, LED17, LED18, LED19, LED20, LED21, LED22, LED23, LED24, LED25, LED26, LED27, LED28, LED29, LED30, LED31, LED32, LED33, LED34, LED35, LED36, LED37, LED38, LED39, LED40, LED41, LED42, LED43, LED44, LED45, LED46, LED47, LED48, LED49, LED50, LED51, LED52, LED53, LED54, LED55, LED56, LED57, LED58, LED59, LED60, LED61, LED62, LED63, LED64, LED65, LED66, LED67, LED68, LED69, LED70, LED71, LED72</t>
-  </si>
-  <si>
-    <t>R1, R2, R3, R4, R5, R6, R7, R8, R9, R10, R11, R12, R13, R14, R15, R16, R17, R18, R19, R20, R21, R22, R23, R24, R25, R26, R27, R28, R29, R30, R31, R32, R33, R34, R35, R36</t>
-  </si>
-  <si>
-    <t>LED 0201</t>
-  </si>
-  <si>
-    <t>RC0402FR-07200RL</t>
-  </si>
-  <si>
-    <t>RES 0402</t>
-  </si>
-  <si>
-    <t>KTRLIGHT</t>
-  </si>
-  <si>
-    <t>KTRLIGHT 0201 SMD LED Red 620-625nm 0.06W high bright quality 0201 Led chip led lamp beads surface mounted SMD LED datasheet</t>
-  </si>
-  <si>
-    <t>RES 200 OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
     <t>Custom Supplier</t>
+  </si>
+  <si>
+    <t>SMD,3.5x3.5mm Light Emitting Diodes (LED) RoHS</t>
+  </si>
+  <si>
+    <t>LED0, LED1, LED2, LED3, LED4, LED5, LED6, LED7, LED8, LED9, LED10, LED11, LED12, LED13</t>
+  </si>
+  <si>
+    <t>WS2812B-Mini</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Worldsemi</t>
+  </si>
+  <si>
+    <t>CC0201KRX5R6BB104</t>
+  </si>
+  <si>
+    <t>CAP 0201</t>
+  </si>
+  <si>
+    <t>C1, C2, C3, C4, C5, C6, C7, C8, C9, C10, C11, C12, C13, C14</t>
+  </si>
+  <si>
+    <t>Cap Ceramic 0.1uF 10V X5R 10% SMD 0201 85C Paper T/R</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>0.1uF</t>
+  </si>
+  <si>
+    <t>Connector</t>
+  </si>
+  <si>
+    <t>3 POS 2.54mm female header</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">801-47-003-10-001000
+</t>
+  </si>
+  <si>
+    <t>Mill-Max</t>
   </si>
 </sst>
 </file>
@@ -240,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -293,7 +312,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -314,67 +348,9 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -394,6 +370,96 @@
         <color indexed="64"/>
       </left>
       <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -409,8 +475,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -420,85 +539,72 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -815,12 +921,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB8DC2DF-2E77-49C4-9458-84630AD19973}">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
     <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="35.42578125" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="27.7109375" customWidth="1"/>
@@ -838,223 +944,277 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
+      <c r="A1" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="210.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+    <row r="3" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="15">
+        <v>14</v>
+      </c>
+      <c r="K3" s="16">
+        <f>J3*5</f>
+        <v>70</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="6">
+        <v>1.05</v>
+      </c>
+      <c r="N3" s="5">
+        <f>M3*J3</f>
+        <v>14.700000000000001</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0.78</v>
+      </c>
+      <c r="P3" s="5">
+        <f>O3*K3</f>
+        <v>54.6</v>
+      </c>
+      <c r="Q3" s="7"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="36">
+        <v>1</v>
+      </c>
+      <c r="K4" s="37">
+        <f>J4*5</f>
+        <v>5</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="31">
+        <v>1.02</v>
+      </c>
+      <c r="N4" s="32">
+        <f t="shared" ref="N4" si="0">M4*J4</f>
+        <v>1.02</v>
+      </c>
+      <c r="O4" s="31">
+        <v>1.02</v>
+      </c>
+      <c r="P4" s="32">
+        <f t="shared" ref="P4" si="1">O4*K4</f>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Q4" s="38"/>
+    </row>
+    <row r="5" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="45">
+        <v>3</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="25" t="s">
+      <c r="E5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="26">
-        <v>72</v>
-      </c>
-      <c r="K3" s="27">
-        <f>J3*5</f>
-        <v>360</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="9">
-        <v>0.47</v>
-      </c>
-      <c r="N3" s="8">
-        <f>M3*J3</f>
-        <v>33.839999999999996</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="P3" s="8">
-        <f>O3*K3</f>
-        <v>100.80000000000001</v>
-      </c>
-      <c r="Q3" s="10"/>
+      <c r="F5" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="19">
+        <v>14</v>
+      </c>
+      <c r="K5" s="43">
+        <f t="shared" ref="K5" si="2">J5*5</f>
+        <v>70</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="44">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" ref="N5" si="3">M5*J5</f>
+        <v>0.504</v>
+      </c>
+      <c r="O5" s="44">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="P5" s="9">
+        <f>(O5*50)+(M5*20)</f>
+        <v>1.71</v>
+      </c>
+      <c r="Q5" s="10"/>
     </row>
-    <row r="4" spans="1:17" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" s="16" t="s">
+    <row r="6" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I6" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="31">
-        <v>36</v>
-      </c>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4" si="0">J4*5</f>
-        <v>180</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" s="14">
-        <v>1.6E-2</v>
-      </c>
-      <c r="N4" s="15">
-        <f t="shared" ref="N4" si="1">M4*J4</f>
-        <v>0.57600000000000007</v>
-      </c>
-      <c r="O4" s="14">
-        <v>6.6E-3</v>
-      </c>
-      <c r="P4" s="15">
-        <f t="shared" ref="P4" si="2">O4*K4</f>
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="Q4" s="19"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="N6" s="13">
+        <f>SUM(N3:N5)</f>
+        <v>16.224</v>
+      </c>
+      <c r="P6" s="13">
+        <f>SUM(P3:P5)</f>
+        <v>61.410000000000004</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="I5" s="17" t="s">
+    <row r="7" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="I7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="N5" s="22">
-        <f>SUM(N3:N4)</f>
-        <v>34.415999999999997</v>
-      </c>
-      <c r="P5" s="22">
-        <f>SUM(P3:P4)</f>
-        <v>101.98800000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="I6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="21">
-        <f>SUM(M3:M4)</f>
-        <v>0.48599999999999999</v>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="12">
+        <f>SUM(M3:M5)</f>
+        <v>2.1060000000000003</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="I5:L5"/>
     <mergeCell ref="I6:L6"/>
+    <mergeCell ref="I7:L7"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3:K4">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="J3:K5">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1065,8 +1225,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N4">
-    <cfRule type="dataBar" priority="5">
+  <conditionalFormatting sqref="N3 N5">
+    <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1079,8 +1239,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P4">
-    <cfRule type="dataBar" priority="6">
+  <conditionalFormatting sqref="P3 P5">
+    <cfRule type="dataBar" priority="8">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1093,10 +1253,40 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N4">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{806F8C3A-2BBB-4280-BC8D-A451438A126E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P4">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFD6007B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5104B2EA-F186-4759-B600-C59CC9631544}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L4" r:id="rId1" xr:uid="{89E528AF-9785-40E1-867E-0BB61CE2B06F}"/>
+    <hyperlink ref="L5" r:id="rId1" xr:uid="{89E528AF-9785-40E1-867E-0BB61CE2B06F}"/>
+    <hyperlink ref="L4" r:id="rId2" xr:uid="{0F30DC65-CD63-4CB2-AAFB-E83617BA0BA7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1111,7 +1301,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N4</xm:sqref>
+          <xm:sqref>N3 N5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{04B48C96-E7CF-4070-AC38-040339A80186}">
@@ -1124,7 +1314,33 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P4</xm:sqref>
+          <xm:sqref>P3 P5</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{806F8C3A-2BBB-4280-BC8D-A451438A126E}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N4</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5104B2EA-F186-4759-B600-C59CC9631544}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFD6007B"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P4</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
